--- a/Additional_UI_Findings_Template.xlsx
+++ b/Additional_UI_Findings_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B7A3DF-E7AD-4A86-8417-B61176F5D798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE903F7-730A-41D1-8954-2486D8853AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
   <si>
     <t>S.No</t>
   </si>
@@ -272,12 +272,24 @@
   <si>
     <t>Fix the View List navigation so it opens the correct list details page instead of showing 404.</t>
   </si>
+  <si>
+    <t>Team Lists</t>
+  </si>
+  <si>
+    <t>UI Bug</t>
+  </si>
+  <si>
+    <t>The list name "Regional Leadership Committee (Current)" is overflowing outside the table/container area, causing the dropdown/column options to be partially hidden.</t>
+  </si>
+  <si>
+    <t>Apply proper text wrapping or truncation with tooltip, and ensure dropdown menus render above the table without being hidden by overflow.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -298,6 +310,10 @@
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -330,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -348,6 +364,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -935,15 +954,29 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="54.95" customHeight="1">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="F20" s="3"/>
     </row>
@@ -1036,25 +1069,25 @@
       <c r="F31" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F19:F31">
+  <conditionalFormatting sqref="F20:F31">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>F19="Open"</formula>
+      <formula>F20="Open"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>F19="Blocked"</formula>
+      <formula>F20="Blocked"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>F19="Pending Clarification"</formula>
+      <formula>F20="Pending Clarification"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>F19="Closed"</formula>
+      <formula>F20="Closed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C19:C31" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C20:C31" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Bug,Enhancement,Missing Feature,Access/Permission,Clarification Needed,Blocked / Access"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F19:F31" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="F20:F31" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Open,Blocked,Pending Clarification,Closed,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
